--- a/data/Lead_information_Formulario_Peru_Main.xlsx
+++ b/data/Lead_information_Formulario_Peru_Main.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.pe/lanzamiento-revelacion-sonic</t>
+          <t>https://www.chevrolet.com.pe/evento-agrofest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/peru/gm_forms/sonic?model=sonic</t>
+          <t>https://secure-developments.com/commonwealth/peru/gm_forms/agrofest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -502,23 +502,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Castillo</t>
+          <t>Jimenez</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10324940</t>
+          <t>98888916</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>989594775</t>
+          <t>917619924</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>valeriacastillo_pe59@mrm.com</t>
+          <t>valeriajimenez_pe72@mrm.com</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -529,39 +529,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.pe/vehiculos-hibridos/captiva-phev</t>
+          <t>https://www.chevrolet.com.pe/reactiva-tu-garantia</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/peru/gm_forms/captiva-hibrida?model=captiva%20hibrida</t>
+          <t>https://secure-developments.com/commonwealth/peru/gm_forms/airlife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Luis Valentina</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gonzalez Contreras</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>39967836</t>
+          <t>57577243</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>928981913</t>
+          <t>930693292</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>luisvalentinagonzalezcontreras.pe92@mrm.com</t>
+          <t>monicaramos_pe33@mrm.com</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -572,39 +572,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.pe/vehiculos-electricos/spark-euv/accesorios/formulario</t>
+          <t>https://www.chevrolet.com.pe/colision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/peru/gm_forms/accesorios?model=spark%20euv</t>
+          <t>https://secure-developments.com/commonwealth/peru/gm_forms/colision</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Patricia Felipe</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5086076</t>
+          <t>67467169</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>979100363</t>
+          <t>913637833</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>patriciafelipemedina_pe70@mrm.com</t>
+          <t>juanmiranda_pe96@mrm.com</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -626,28 +626,28 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Eduardo Camila</t>
+          <t>Juan Andrea</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>33493300</t>
+          <t>62842135</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>919207529</t>
+          <t>937986808</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>eduardocamilacontreras_pe60@mrm.com</t>
+          <t>juanandreaserrano_pe45@mrm.com</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -669,28 +669,28 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pablo Cristian</t>
+          <t>Martín</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bravo Mora</t>
+          <t>Pinto Ramirez</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>78970751</t>
+          <t>68349647</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>957100485</t>
+          <t>937159678</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>pablocristianbravomora_pe41@mrm.com</t>
+          <t>martinpintoramirez_pe44@mrm.com</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>

--- a/data/Lead_information_Formulario_Peru_Main.xlsx
+++ b/data/Lead_information_Formulario_Peru_Main.xlsx
@@ -497,28 +497,28 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Gabriela Andrea</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jimenez</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>98888916</t>
+          <t>34446200</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>917619924</t>
+          <t>987307159</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>valeriajimenez_pe72@mrm.com</t>
+          <t>gabrielaandreamora_pe54@mrm.com</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -529,39 +529,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.pe/reactiva-tu-garantia</t>
+          <t>https://www.chevrolet.com.pe/lanzamiento-revelacion-sonic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/peru/gm_forms/airlife</t>
+          <t>https://secure-developments.com/commonwealth/peru/gm_forms/sonic?model=sonic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Mendoza Espinoza</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57577243</t>
+          <t>86892644</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>930693292</t>
+          <t>980371444</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>monicaramos_pe33@mrm.com</t>
+          <t>isabellamendozaespinoza.pe55@mrm.com</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -572,39 +572,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.pe/colision</t>
+          <t>https://www.chevrolet.com.pe/vehiculos-electricos/spark-euv/accesorios/formulario</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/peru/gm_forms/colision</t>
+          <t>https://secure-developments.com/commonwealth/peru/gm_forms/accesorios?model=spark%20euv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Reyes Ruiz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67467169</t>
+          <t>16256468</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>913637833</t>
+          <t>930118730</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>juanmiranda_pe96@mrm.com</t>
+          <t>gabrielreyesruiz.pe46@mrm.com</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -626,28 +626,28 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Juan Andrea</t>
+          <t>Andrés</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Vega Perez</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>62842135</t>
+          <t>74125182</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>937986808</t>
+          <t>994291301</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>juanandreaserrano_pe45@mrm.com</t>
+          <t>andresvegaperez_pe50@mrm.com</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -669,28 +669,28 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Martín</t>
+          <t>Romina Ana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pinto Ramirez</t>
+          <t>Medina Suarez</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>68349647</t>
+          <t>28923487</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>937159678</t>
+          <t>962225433</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>martinpintoramirez_pe44@mrm.com</t>
+          <t>rominaanamedinasuarez.pe49@mrm.com</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
